--- a/source/xlsx/A2/unit-4/Deutsch_Heimkehr_A2_U4_Review_v1.0.xlsx
+++ b/source/xlsx/A2/unit-4/Deutsch_Heimkehr_A2_U4_Review_v1.0.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lesson" sheetId="1" r:id="R6fd0f04684a14f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary" sheetId="2" r:id="Ra6c6c2693df3401e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grammar" sheetId="3" r:id="R2025d5a2a2fb44ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogue" sheetId="4" r:id="R06bb886b59b54d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice" sheetId="5" r:id="Rfab1ab2e65934b6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="6" r:id="R71c7edf7d9d44a4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lesson" sheetId="1" r:id="R18715e31949a413d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary" sheetId="2" r:id="R7fd62a845f414ba8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grammar" sheetId="3" r:id="Rcf63b6de750a4976"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogue" sheetId="4" r:id="R3b3f3599e1fe4865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice" sheetId="5" r:id="R3f8a93af73544bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="6" r:id="R1185543a9add4ed2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -56,8 +56,14 @@
       <x:sz val="13"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -79,6 +85,11 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -88,7 +99,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="61">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -180,6 +191,73 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1571,188 +1649,383 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="100" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="3" width="28" customWidth="1"/>
+    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" customHeight="1">
-      <x:c r="A1" s="13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dialogue 1 – Apartment Viewing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="5" t="n"/>
-      <x:c r="C1" s="5" t="n"/>
+      <x:c r="A1" s="56" t="str">
+        <x:v>Speaker</x:v>
+      </x:c>
+      <x:c r="B1" s="57" t="str">
+        <x:v>German</x:v>
+      </x:c>
+      <x:c r="C1" s="57" t="str">
+        <x:v>English</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="85.5" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Anna: Guten Tag. Ist die Wohnung noch frei?
-Vermieter: Ja, möchten Sie sie besichtigen?
-Anna: Ja, wie hoch ist die Warmmiete?
-Vermieter: Sie beträgt 920 Euro im Monat.
-Anna: Sind die Nebenkosten enthalten?
-Vermieter: Ja, Heizung und Wasser sind inklusive.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="n"/>
-      <x:c r="C2" s="2" t="n"/>
+      <x:c r="A2" s="58" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="B2" s="59" t="str">
+        <x:v>Dialogue 1 – Apartment Viewing</x:v>
+      </x:c>
+      <x:c r="C2" s="59" t="str">
+        <x:v>Dialogue 1 – Apartment Viewing</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="28.5" customHeight="1">
-      <x:c r="A3" s="8" t="n"/>
-      <x:c r="B3" s="2" t="n"/>
-      <x:c r="C3" s="2" t="n"/>
+      <x:c r="A3" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B3" s="59" t="str">
+        <x:v>Guten Tag. Ist die Wohnung noch frei?</x:v>
+      </x:c>
+      <x:c r="C3" s="59" t="str">
+        <x:v>Good afternoon. Is the apartment still available?</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="2" t="n"/>
-      <x:c r="B4" s="2" t="n"/>
-      <x:c r="C4" s="2" t="n"/>
+      <x:c r="A4" s="58" t="str">
+        <x:v>Vermieter</x:v>
+      </x:c>
+      <x:c r="B4" s="59" t="str">
+        <x:v>Ja, möchten Sie sie besichtigen?</x:v>
+      </x:c>
+      <x:c r="C4" s="59" t="str">
+        <x:v>Yes. Would you like to view it?</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="2" t="n"/>
-      <x:c r="B5" s="2" t="n"/>
-      <x:c r="C5" s="2" t="n"/>
+      <x:c r="A5" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B5" s="59" t="str">
+        <x:v>Ja, wie hoch ist die Warmmiete?</x:v>
+      </x:c>
+      <x:c r="C5" s="59" t="str">
+        <x:v>Yes. How much is the warm rent?</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="2" t="n"/>
-      <x:c r="B6" s="2" t="n"/>
-      <x:c r="C6" s="2" t="n"/>
+      <x:c r="A6" s="58" t="str">
+        <x:v>Vermieter</x:v>
+      </x:c>
+      <x:c r="B6" s="59" t="str">
+        <x:v>Sie beträgt 920 Euro im Monat.</x:v>
+      </x:c>
+      <x:c r="C6" s="59" t="str">
+        <x:v>It amounts to 920 euros per month.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="16.5" customHeight="1">
-      <x:c r="A7" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dialogue 2 – Signing the Lease</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="2" t="n"/>
-      <x:c r="C7" s="2" t="n"/>
+      <x:c r="A7" s="60" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B7" s="59" t="str">
+        <x:v>Sind die Nebenkosten enthalten?</x:v>
+      </x:c>
+      <x:c r="C7" s="59" t="str">
+        <x:v>Are the additional costs included?</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="57" customHeight="1">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Vermieter: Haben Sie den Mietvertrag gelesen?
-Anna: Ja, alles sieht gut aus.
-Vermieter: Die Kaution beträgt zwei Monatsmieten.
-Anna: Kein Problem. Ich unterschreibe heute.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="2" t="n"/>
-      <x:c r="C8" s="2" t="n"/>
+      <x:c r="A8" s="58" t="str">
+        <x:v>Vermieter</x:v>
+      </x:c>
+      <x:c r="B8" s="59" t="str">
+        <x:v>Ja, Heizung und Wasser sind inklusive.</x:v>
+      </x:c>
+      <x:c r="C8" s="59" t="str">
+        <x:v>Yes. Heating and water are included.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="2" t="n"/>
-      <x:c r="B9" s="2" t="n"/>
-      <x:c r="C9" s="2" t="n"/>
+      <x:c r="A9" s="58" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="B9" s="59" t="str">
+        <x:v>Dialogue 2 – Signing the Lease</x:v>
+      </x:c>
+      <x:c r="C9" s="59" t="str">
+        <x:v>Dialogue 2 – Signing the Lease</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="2" t="n"/>
-      <x:c r="B10" s="2" t="n"/>
-      <x:c r="C10" s="2" t="n"/>
+      <x:c r="A10" s="58" t="str">
+        <x:v>Vermieter</x:v>
+      </x:c>
+      <x:c r="B10" s="59" t="str">
+        <x:v>Haben Sie den Mietvertrag gelesen?</x:v>
+      </x:c>
+      <x:c r="C10" s="59" t="str">
+        <x:v>Have you read the lease?</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="2" t="n"/>
-      <x:c r="B11" s="2" t="n"/>
-      <x:c r="C11" s="2" t="n"/>
+      <x:c r="A11" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B11" s="59" t="str">
+        <x:v>Ja, alles sieht gut aus.</x:v>
+      </x:c>
+      <x:c r="C11" s="59" t="str">
+        <x:v>Yes. Everything looks good.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="2" t="n"/>
-      <x:c r="B12" s="2" t="n"/>
-      <x:c r="C12" s="2" t="n"/>
+      <x:c r="A12" s="58" t="str">
+        <x:v>Vermieter</x:v>
+      </x:c>
+      <x:c r="B12" s="59" t="str">
+        <x:v>Die Kaution beträgt zwei Monatsmieten.</x:v>
+      </x:c>
+      <x:c r="C12" s="59" t="str">
+        <x:v>The deposit amounts to two months' rent.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="16.5" customHeight="1">
-      <x:c r="A13" s="14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dialogue 3 – Utilities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="2" t="n"/>
-      <x:c r="C13" s="2" t="n"/>
+      <x:c r="A13" s="60" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B13" s="59" t="str">
+        <x:v>Kein Problem. Ich unterschreibe heute.</x:v>
+      </x:c>
+      <x:c r="C13" s="59" t="str">
+        <x:v>No problem. I will sign today.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="60" customHeight="1">
-      <x:c r="A14" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Anna: Funktioniert das WLAN schon?
-Hausmeister: Der Router ist installiert, aber Sie müssen ihn noch einrichten.
-Anna: Danke. Wo finde ich den Briefkasten?
-Hausmeister: Direkt neben dem Haupteingang.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="2" t="n"/>
-      <x:c r="C14" s="2" t="n"/>
+      <x:c r="A14" s="58" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="B14" s="59" t="str">
+        <x:v>Dialogue 3 – Utilities</x:v>
+      </x:c>
+      <x:c r="C14" s="59" t="str">
+        <x:v>Dialogue 3 – Utilities</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="2" t="n"/>
-      <x:c r="B15" s="2" t="n"/>
-      <x:c r="C15" s="2" t="n"/>
+      <x:c r="A15" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B15" s="59" t="str">
+        <x:v>Funktioniert das WLAN schon?</x:v>
+      </x:c>
+      <x:c r="C15" s="59" t="str">
+        <x:v>Is the Wi-Fi working yet?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="58" t="str">
+        <x:v>Hausmeister</x:v>
+      </x:c>
+      <x:c r="B16" s="59" t="str">
+        <x:v>Der Router ist installiert, aber Sie müssen ihn noch einrichten.</x:v>
+      </x:c>
+      <x:c r="C16" s="59" t="str">
+        <x:v>The router is installed, but you still need to set it up.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B17" s="59" t="str">
+        <x:v>Danke. Wo finde ich den Briefkasten?</x:v>
+      </x:c>
+      <x:c r="C17" s="59" t="str">
+        <x:v>Thank you. Where can I find the mailbox?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="58" t="str">
+        <x:v>Hausmeister</x:v>
+      </x:c>
+      <x:c r="B18" s="59" t="str">
+        <x:v>Direkt neben dem Haupteingang.</x:v>
+      </x:c>
+      <x:c r="C18" s="59" t="str">
+        <x:v>Directly beside the main entrance.</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="16.5" customHeight="1">
-      <x:c r="A19" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dialogue 4 – Reporting a Repair</x:t>
-        </x:is>
+      <x:c r="A19" s="60" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="B19" s="59" t="str">
+        <x:v>Dialogue 4 – Reporting a Repair</x:v>
+      </x:c>
+      <x:c r="C19" s="59" t="str">
+        <x:v>Dialogue 4 – Reporting a Repair</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Anna: Guten Morgen. Die Heizung funktioniert nicht.
-Vermieter: Ich schicke heute einen Techniker.
-Anna: Vielen Dank. Hoffentlich ist sie bald repariert.
-Vermieter: Ich melde mich später noch einmal.</x:t>
-        </x:is>
+      <x:c r="A20" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B20" s="59" t="str">
+        <x:v>Guten Morgen. Die Heizung funktioniert nicht.</x:v>
+      </x:c>
+      <x:c r="C20" s="59" t="str">
+        <x:v>Good morning. The heating is not working.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" customHeight="1">
-      <x:c r="A21" s="9" t="n"/>
+      <x:c r="A21" s="58" t="str">
+        <x:v>Vermieter</x:v>
+      </x:c>
+      <x:c r="B21" s="59" t="str">
+        <x:v>Ich schicke heute einen Techniker.</x:v>
+      </x:c>
+      <x:c r="C21" s="59" t="str">
+        <x:v>I will send a technician today.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B22" s="59" t="str">
+        <x:v>Vielen Dank. Hoffentlich ist sie bald repariert.</x:v>
+      </x:c>
+      <x:c r="C22" s="59" t="str">
+        <x:v>Thank you very much. Hopefully it will be repaired soon.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="58" t="str">
+        <x:v>Vermieter</x:v>
+      </x:c>
+      <x:c r="B23" s="59" t="str">
+        <x:v>Ich melde mich später noch einmal.</x:v>
+      </x:c>
+      <x:c r="C23" s="59" t="str">
+        <x:v>I will contact you again later.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="58" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="B24" s="59" t="str">
+        <x:v>Dialogue 5 – Safety and Building Rules</x:v>
+      </x:c>
+      <x:c r="C24" s="59" t="str">
+        <x:v>Dialogue 5 – Safety and Building Rules</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="16.5" customHeight="1">
-      <x:c r="A25" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dialogue 5 – Safety and Building Rules</x:t>
-        </x:is>
+      <x:c r="A25" s="60" t="str">
+        <x:v>Nachbar</x:v>
+      </x:c>
+      <x:c r="B25" s="59" t="str">
+        <x:v>Kennen Sie schon die Hausordnung?</x:v>
+      </x:c>
+      <x:c r="C25" s="59" t="str">
+        <x:v>Are you already familiar with the house rules?</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nachbar: Kennen Sie schon die Hausordnung?
-Anna: Noch nicht ganz.
-Nachbar: Bitte beachten Sie die Ruhezeit und trennen Sie den Müll.
-Anna: Danke für den Hinweis!</x:t>
-        </x:is>
+      <x:c r="A26" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B26" s="59" t="str">
+        <x:v>Noch nicht ganz.</x:v>
+      </x:c>
+      <x:c r="C26" s="59" t="str">
+        <x:v>Not completely yet.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" customHeight="1">
-      <x:c r="A27" s="9" t="n"/>
+      <x:c r="A27" s="58" t="str">
+        <x:v>Nachbar</x:v>
+      </x:c>
+      <x:c r="B27" s="59" t="str">
+        <x:v>Bitte beachten Sie die Ruhezeit und trennen Sie den Müll.</x:v>
+      </x:c>
+      <x:c r="C27" s="59" t="str">
+        <x:v>Please observe the quiet hours and separate the trash.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B28" s="59" t="str">
+        <x:v>Danke für den Hinweis!</x:v>
+      </x:c>
+      <x:c r="C28" s="59" t="str">
+        <x:v>Thank you for the information!</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="15" customHeight="1">
-      <x:c r="A29" s="9" t="n"/>
+      <x:c r="A29" s="58" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="B29" s="59" t="str">
+        <x:v>Review Conversation</x:v>
+      </x:c>
+      <x:c r="C29" s="59" t="str">
+        <x:v>Review Conversation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="58" t="str">
+        <x:v>Freund</x:v>
+      </x:c>
+      <x:c r="B30" s="59" t="str">
+        <x:v>Wie gefällt dir deine neue Wohnung?</x:v>
+      </x:c>
+      <x:c r="C30" s="59" t="str">
+        <x:v>How do you like your new apartment?</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="16.5" customHeight="1">
-      <x:c r="A31" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Review Conversation</x:t>
-        </x:is>
+      <x:c r="A31" s="60" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B31" s="59" t="str">
+        <x:v>Sehr gut! Ich habe den Mietvertrag unterschrieben, das WLAN funktioniert und alle Nachbarn sind freundlich.</x:v>
+      </x:c>
+      <x:c r="C31" s="59" t="str">
+        <x:v>Very much! I signed the lease, the Wi-Fi works, and all the neighbors are friendly.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Freund: Wie gefällt dir deine neue Wohnung?
-Anna: Sehr gut! Ich habe den Mietvertrag unterschrieben, das WLAN funktioniert und alle Nachbarn sind freundlich.
-Freund: Dann bist du gut in Deutschland angekommen!
-Anna: Ja, ich fühle mich schon wie zu Hause.</x:t>
-        </x:is>
+      <x:c r="A32" s="58" t="str">
+        <x:v>Freund</x:v>
+      </x:c>
+      <x:c r="B32" s="59" t="str">
+        <x:v>Dann bist du gut in Deutschland angekommen!</x:v>
+      </x:c>
+      <x:c r="C32" s="59" t="str">
+        <x:v>Then you have settled into Germany well!</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="58" t="str">
+        <x:v>Anna</x:v>
+      </x:c>
+      <x:c r="B33" s="59" t="str">
+        <x:v>Ja, ich fühle mich schon wie zu Hause.</x:v>
+      </x:c>
+      <x:c r="C33" s="59" t="str">
+        <x:v>Yes, I already feel at home.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" customHeight="1">
-      <x:c r="A35" s="9" t="n"/>
+      <x:c r="A35" s="9"/>
     </x:row>
     <x:row r="42" ht="15" customHeight="1">
-      <x:c r="A42" s="9" t="n"/>
+      <x:c r="A42" s="9"/>
     </x:row>
     <x:row r="49" ht="15" customHeight="1">
-      <x:c r="A49" s="9" t="n"/>
+      <x:c r="A49" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/xlsx/A2/unit-4/Deutsch_Heimkehr_A2_U4_Review_v1.0.xlsx
+++ b/source/xlsx/A2/unit-4/Deutsch_Heimkehr_A2_U4_Review_v1.0.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lesson" sheetId="1" r:id="R796e632201bb4a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary" sheetId="2" r:id="Re2b6c5d50640445d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grammar" sheetId="3" r:id="Ref4c061eaa594686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogue" sheetId="4" r:id="R1ccbdab6bc284153"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice" sheetId="5" r:id="R47e3fd06c19b4150"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="6" r:id="R0b08622fd8ec4e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lesson" sheetId="1" r:id="Rec3629b57e474324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary" sheetId="2" r:id="Rac423be7cd674349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grammar" sheetId="3" r:id="Rbb7ae450a36e400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogue" sheetId="4" r:id="R0d3f3c8e2fdb498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Practice" sheetId="5" r:id="R31660c14b2a24384"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="6" r:id="Rd650c1fb48224bb2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2686,9 +2686,7 @@
       <x:c r="E3" s="59" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F3" s="59" t="str">
-        <x:v>Kaution</x:v>
-      </x:c>
+      <x:c r="F3" s="59"/>
       <x:c r="G3" s="59" t="str">
         <x:v>Heizung</x:v>
       </x:c>
@@ -2702,7 +2700,7 @@
         <x:v>Kaution</x:v>
       </x:c>
       <x:c r="K3" s="59" t="str">
-        <x:v>D</x:v>
+        <x:v>Kaution</x:v>
       </x:c>
       <x:c r="L3" s="59" t="str">
         <x:v>The security deposit (Kaution) is paid separately and is not part of the monthly Warmmiete.</x:v>
@@ -2725,9 +2723,7 @@
       <x:c r="E4" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F4" s="61" t="str">
-        <x:v>Wie hoch ist die Warmmiete?</x:v>
-      </x:c>
+      <x:c r="F4" s="61"/>
       <x:c r="G4" s="61" t="str">
         <x:v>Wo ist der Balkon?</x:v>
       </x:c>
@@ -2741,7 +2737,7 @@
         <x:v>Gibt es einen Keller?</x:v>
       </x:c>
       <x:c r="K4" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Wie hoch ist die Warmmiete?</x:v>
       </x:c>
       <x:c r="L4" s="61" t="str">
         <x:v>Asking about the Warmmiete lets you compare the total monthly housing cost.</x:v>
@@ -2764,9 +2760,7 @@
       <x:c r="E5" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F5" s="61" t="str">
-        <x:v>Pay rent on time; Report major damage; Respect Ruhezeit</x:v>
-      </x:c>
+      <x:c r="F5" s="61"/>
       <x:c r="G5" s="61" t="str">
         <x:v>Pay rent on time</x:v>
       </x:c>
@@ -2780,7 +2774,7 @@
         <x:v>Approve structural repairs</x:v>
       </x:c>
       <x:c r="K5" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Pay rent on time; Report major damage; Respect Ruhezeit</x:v>
       </x:c>
       <x:c r="L5" s="61" t="str">
         <x:v>Tenants should pay rent, report problems, and follow building rules. Major structural repairs are generally the landlord's responsibility.</x:v>
@@ -2803,9 +2797,7 @@
       <x:c r="E6" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F6" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F6" s="61"/>
       <x:c r="G6" s="61"/>
       <x:c r="H6" s="61"/>
       <x:c r="I6" s="61"/>
@@ -2834,9 +2826,7 @@
       <x:c r="E7" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F7" s="61" t="str">
-        <x:v>Mietvertrag</x:v>
-      </x:c>
+      <x:c r="F7" s="61"/>
       <x:c r="G7" s="61"/>
       <x:c r="H7" s="61"/>
       <x:c r="I7" s="61"/>
@@ -2865,9 +2855,7 @@
       <x:c r="E8" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F8" s="61" t="str">
-        <x:v>Sind Haustiere erlaubt?</x:v>
-      </x:c>
+      <x:c r="F8" s="61"/>
       <x:c r="G8" s="61" t="str">
         <x:v>Wo ist der Bahnhof?</x:v>
       </x:c>
@@ -2881,7 +2869,7 @@
         <x:v>Wie ist das Wetter?</x:v>
       </x:c>
       <x:c r="K8" s="61" t="str">
-        <x:v>B</x:v>
+        <x:v>Sind Haustiere erlaubt?</x:v>
       </x:c>
       <x:c r="L8" s="61" t="str">
         <x:v>Questions about the rental conditions help you decide whether the apartment fits your needs.</x:v>
@@ -2903,9 +2891,7 @@
       <x:c r="E9" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F9" s="61" t="str">
-        <x:v>Heizung; Wasser; Nebenkosten</x:v>
-      </x:c>
+      <x:c r="F9" s="61"/>
       <x:c r="G9" s="61" t="str">
         <x:v>Heizung</x:v>
       </x:c>
@@ -2919,7 +2905,7 @@
         <x:v>Kaution</x:v>
       </x:c>
       <x:c r="K9" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Heizung; Wasser; Nebenkosten</x:v>
       </x:c>
       <x:c r="L9" s="61" t="str">
         <x:v>Warmmiete often includes several operating costs, but not the deposit.</x:v>
@@ -2941,9 +2927,7 @@
       <x:c r="E10" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F10" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F10" s="61"/>
       <x:c r="G10" s="61"/>
       <x:c r="H10" s="61"/>
       <x:c r="I10" s="61"/>
@@ -2971,9 +2955,7 @@
       <x:c r="E11" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F11" s="61" t="str">
-        <x:v>Vermieter</x:v>
-      </x:c>
+      <x:c r="F11" s="61"/>
       <x:c r="G11" s="61"/>
       <x:c r="H11" s="61"/>
       <x:c r="I11" s="61"/>
@@ -3001,9 +2983,7 @@
       <x:c r="E12" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F12" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F12" s="61"/>
       <x:c r="G12" s="61"/>
       <x:c r="H12" s="61"/>
       <x:c r="I12" s="61"/>
@@ -3031,9 +3011,7 @@
       <x:c r="E13" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F13" s="61" t="str">
-        <x:v>besichtigen</x:v>
-      </x:c>
+      <x:c r="F13" s="61"/>
       <x:c r="G13" s="61"/>
       <x:c r="H13" s="61"/>
       <x:c r="I13" s="61"/>
@@ -3061,9 +3039,7 @@
       <x:c r="E14" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F14" s="61" t="str">
-        <x:v>Router; WLAN</x:v>
-      </x:c>
+      <x:c r="F14" s="61"/>
       <x:c r="G14" s="61" t="str">
         <x:v>Router</x:v>
       </x:c>
@@ -3077,7 +3053,7 @@
         <x:v>Kühlschrank</x:v>
       </x:c>
       <x:c r="K14" s="61" t="str">
-        <x:v>A,B</x:v>
+        <x:v>Router; WLAN</x:v>
       </x:c>
       <x:c r="L14" s="61" t="str">
         <x:v>Router and WLAN relate directly to internet service.</x:v>
@@ -3099,9 +3075,7 @@
       <x:c r="E15" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F15" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F15" s="61"/>
       <x:c r="G15" s="61"/>
       <x:c r="H15" s="61"/>
       <x:c r="I15" s="61"/>
@@ -3129,9 +3103,7 @@
       <x:c r="E16" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F16" s="61" t="str">
-        <x:v>kaputt</x:v>
-      </x:c>
+      <x:c r="F16" s="61"/>
       <x:c r="G16" s="61"/>
       <x:c r="H16" s="61"/>
       <x:c r="I16" s="61"/>
@@ -3159,9 +3131,7 @@
       <x:c r="E17" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F17" s="61" t="str">
-        <x:v>Elektriker</x:v>
-      </x:c>
+      <x:c r="F17" s="61"/>
       <x:c r="G17" s="61" t="str">
         <x:v>Hausmeister</x:v>
       </x:c>
@@ -3175,7 +3145,7 @@
         <x:v>Elektriker</x:v>
       </x:c>
       <x:c r="K17" s="61" t="str">
-        <x:v>D</x:v>
+        <x:v>Elektriker</x:v>
       </x:c>
       <x:c r="L17" s="61" t="str">
         <x:v>An Elektriker repairs electrical systems.</x:v>
@@ -3197,9 +3167,7 @@
       <x:c r="E18" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F18" s="61" t="str">
-        <x:v>Klempner</x:v>
-      </x:c>
+      <x:c r="F18" s="61"/>
       <x:c r="G18" s="61" t="str">
         <x:v>Nachbar</x:v>
       </x:c>
@@ -3213,7 +3181,7 @@
         <x:v>Maler</x:v>
       </x:c>
       <x:c r="K18" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Klempner</x:v>
       </x:c>
       <x:c r="L18" s="61" t="str">
         <x:v>A Klempner repairs plumbing and leaking pipes.</x:v>
@@ -3235,9 +3203,7 @@
       <x:c r="E19" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F19" s="61" t="str">
-        <x:v>Rauchmelder; Feuerlöscher</x:v>
-      </x:c>
+      <x:c r="F19" s="61"/>
       <x:c r="G19" s="61" t="str">
         <x:v>Rauchmelder</x:v>
       </x:c>
@@ -3251,7 +3217,7 @@
         <x:v>Balkon</x:v>
       </x:c>
       <x:c r="K19" s="61" t="str">
-        <x:v>A,B</x:v>
+        <x:v>Rauchmelder; Feuerlöscher</x:v>
       </x:c>
       <x:c r="L19" s="61" t="str">
         <x:v>Smoke detectors and fire extinguishers improve safety.</x:v>
@@ -3273,9 +3239,7 @@
       <x:c r="E20" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F20" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F20" s="61"/>
       <x:c r="G20" s="61"/>
       <x:c r="H20" s="61"/>
       <x:c r="I20" s="61"/>
@@ -3303,9 +3267,7 @@
       <x:c r="E21" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F21" s="61" t="str">
-        <x:v>melden</x:v>
-      </x:c>
+      <x:c r="F21" s="61"/>
       <x:c r="G21" s="61"/>
       <x:c r="H21" s="61"/>
       <x:c r="I21" s="61"/>
@@ -3333,9 +3295,7 @@
       <x:c r="E22" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F22" s="61" t="str">
-        <x:v>Hausratversicherung</x:v>
-      </x:c>
+      <x:c r="F22" s="61"/>
       <x:c r="G22" s="61" t="str">
         <x:v>Krankenversicherung</x:v>
       </x:c>
@@ -3349,7 +3309,7 @@
         <x:v>Haftpflichtversicherung</x:v>
       </x:c>
       <x:c r="K22" s="61" t="str">
-        <x:v>B</x:v>
+        <x:v>Hausratversicherung</x:v>
       </x:c>
       <x:c r="L22" s="61" t="str">
         <x:v>Hausratversicherung protects household belongings against covered losses such as fire, theft, or water damage.</x:v>
@@ -3371,9 +3331,7 @@
       <x:c r="E23" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F23" s="61" t="str">
-        <x:v>Ich muss den Vermieter anrufen.</x:v>
-      </x:c>
+      <x:c r="F23" s="61"/>
       <x:c r="G23" s="61" t="str">
         <x:v>Ich den Vermieter muss anrufen.</x:v>
       </x:c>
@@ -3387,7 +3345,7 @@
         <x:v>Ich muss den Vermieter anrufen.</x:v>
       </x:c>
       <x:c r="K23" s="61" t="str">
-        <x:v>D</x:v>
+        <x:v>Ich muss den Vermieter anrufen.</x:v>
       </x:c>
       <x:c r="L23" s="61" t="str">
         <x:v>'Ich muss den Vermieter anrufen.' correctly uses the modal verb 'müssen' with the infinitive at the end.</x:v>
@@ -3409,9 +3367,7 @@
       <x:c r="E24" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F24" s="61" t="str">
-        <x:v>einziehen; anrufen; abschließen</x:v>
-      </x:c>
+      <x:c r="F24" s="61"/>
       <x:c r="G24" s="61" t="str">
         <x:v>einziehen</x:v>
       </x:c>
@@ -3425,7 +3381,7 @@
         <x:v>abschließen</x:v>
       </x:c>
       <x:c r="K24" s="61" t="str">
-        <x:v>A,B,D</x:v>
+        <x:v>einziehen; anrufen; abschließen</x:v>
       </x:c>
       <x:c r="L24" s="61" t="str">
         <x:v>These verbs separate when conjugated in the present tense.</x:v>
@@ -3447,9 +3403,7 @@
       <x:c r="E25" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F25" s="61" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="F25" s="61"/>
       <x:c r="G25" s="61"/>
       <x:c r="H25" s="61"/>
       <x:c r="I25" s="61"/>
@@ -3477,9 +3431,7 @@
       <x:c r="E26" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F26" s="61" t="str">
-        <x:v>in der</x:v>
-      </x:c>
+      <x:c r="F26" s="61"/>
       <x:c r="G26" s="61"/>
       <x:c r="H26" s="61"/>
       <x:c r="I26" s="61"/>
@@ -3507,9 +3459,7 @@
       <x:c r="E27" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F27" s="61" t="str">
-        <x:v>Ich gehe in die Küche.</x:v>
-      </x:c>
+      <x:c r="F27" s="61"/>
       <x:c r="G27" s="61" t="str">
         <x:v>Die Lampe hängt an der Decke.</x:v>
       </x:c>
@@ -3523,7 +3473,7 @@
         <x:v>Der Tisch steht im Wohnzimmer.</x:v>
       </x:c>
       <x:c r="K27" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Ich gehe in die Küche.</x:v>
       </x:c>
       <x:c r="L27" s="61" t="str">
         <x:v>Movement into a location uses the accusative: 'in die Küche.'</x:v>
@@ -3545,9 +3495,7 @@
       <x:c r="E28" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F28" s="61" t="str">
-        <x:v>in; unter; vor</x:v>
-      </x:c>
+      <x:c r="F28" s="61"/>
       <x:c r="G28" s="61" t="str">
         <x:v>in</x:v>
       </x:c>
@@ -3561,7 +3509,7 @@
         <x:v>vor</x:v>
       </x:c>
       <x:c r="K28" s="61" t="str">
-        <x:v>A,B,D</x:v>
+        <x:v>in; unter; vor</x:v>
       </x:c>
       <x:c r="L28" s="61" t="str">
         <x:v>'Mit' is not a two-way preposition.</x:v>
@@ -3583,9 +3531,7 @@
       <x:c r="E29" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F29" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F29" s="61"/>
       <x:c r="G29" s="61"/>
       <x:c r="H29" s="61"/>
       <x:c r="I29" s="61"/>
@@ -3613,9 +3559,7 @@
       <x:c r="E30" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F30" s="61" t="str">
-        <x:v>haben</x:v>
-      </x:c>
+      <x:c r="F30" s="61"/>
       <x:c r="G30" s="61"/>
       <x:c r="H30" s="61"/>
       <x:c r="I30" s="61"/>
@@ -3643,9 +3587,7 @@
       <x:c r="E31" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F31" s="61" t="str">
-        <x:v>Ich habe den Vertrag unterschrieben.</x:v>
-      </x:c>
+      <x:c r="F31" s="61"/>
       <x:c r="G31" s="61" t="str">
         <x:v>Ich unterschreibe morgen.</x:v>
       </x:c>
@@ -3659,7 +3601,7 @@
         <x:v>Ich unterschreibe den Vertrag.</x:v>
       </x:c>
       <x:c r="K31" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Ich habe den Vertrag unterschrieben.</x:v>
       </x:c>
       <x:c r="L31" s="61" t="str">
         <x:v>The auxiliary verb 'habe' plus the past participle 'unterschrieben' forms the Perfekt.</x:v>
@@ -3681,9 +3623,7 @@
       <x:c r="E32" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F32" s="61" t="str">
-        <x:v>Heizung; Techniker; Klempner</x:v>
-      </x:c>
+      <x:c r="F32" s="61"/>
       <x:c r="G32" s="61" t="str">
         <x:v>Heizung</x:v>
       </x:c>
@@ -3697,7 +3637,7 @@
         <x:v>Briefkasten</x:v>
       </x:c>
       <x:c r="K32" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Heizung; Techniker; Klempner</x:v>
       </x:c>
       <x:c r="L32" s="61" t="str">
         <x:v>Heating, technicians, and plumbers are related to maintenance.</x:v>
@@ -3719,9 +3659,7 @@
       <x:c r="E33" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F33" s="61" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="F33" s="61"/>
       <x:c r="G33" s="61"/>
       <x:c r="H33" s="61"/>
       <x:c r="I33" s="61"/>
@@ -3749,9 +3687,7 @@
       <x:c r="E34" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F34" s="61" t="str">
-        <x:v>Techniker</x:v>
-      </x:c>
+      <x:c r="F34" s="61"/>
       <x:c r="G34" s="61"/>
       <x:c r="H34" s="61"/>
       <x:c r="I34" s="61"/>
@@ -3779,9 +3715,7 @@
       <x:c r="E35" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F35" s="61" t="str">
-        <x:v>Ich fahre morgen mit dem Bus zur Wohnung.</x:v>
-      </x:c>
+      <x:c r="F35" s="61"/>
       <x:c r="G35" s="61" t="str">
         <x:v>Mit dem Bus ich fahre morgen.</x:v>
       </x:c>
@@ -3795,7 +3729,7 @@
         <x:v>Ich fahre mit dem Bus morgen zur Wohnung.</x:v>
       </x:c>
       <x:c r="K35" s="61" t="str">
-        <x:v>B</x:v>
+        <x:v>Ich fahre morgen mit dem Bus zur Wohnung.</x:v>
       </x:c>
       <x:c r="L35" s="61" t="str">
         <x:v>German commonly orders adverbial information as Time–Manner–Place: morgen, mit dem Bus, zur Wohnung.</x:v>
@@ -3817,9 +3751,7 @@
       <x:c r="E36" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F36" s="61" t="str">
-        <x:v>Ist die Wohnung noch frei?; Wie hoch ist die Warmmiete?; Sind die Nebenkosten enthalten?</x:v>
-      </x:c>
+      <x:c r="F36" s="61"/>
       <x:c r="G36" s="61" t="str">
         <x:v>Ist die Wohnung noch frei?</x:v>
       </x:c>
@@ -3833,7 +3765,7 @@
         <x:v>Sind die Nebenkosten enthalten?</x:v>
       </x:c>
       <x:c r="K36" s="61" t="str">
-        <x:v>A,B,D</x:v>
+        <x:v>Ist die Wohnung noch frei?; Wie hoch ist die Warmmiete?; Sind die Nebenkosten enthalten?</x:v>
       </x:c>
       <x:c r="L36" s="61" t="str">
         <x:v>The damage-report phrase belongs to a maintenance situation.</x:v>
@@ -3855,9 +3787,7 @@
       <x:c r="E37" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F37" s="61" t="str">
-        <x:v>Diese Wohnung ist größer als die andere.</x:v>
-      </x:c>
+      <x:c r="F37" s="61"/>
       <x:c r="G37" s="61" t="str">
         <x:v>Diese Wohnung ist groß als die andere.</x:v>
       </x:c>
@@ -3871,7 +3801,7 @@
         <x:v>Diese Wohnung größer als.</x:v>
       </x:c>
       <x:c r="K37" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Diese Wohnung ist größer als die andere.</x:v>
       </x:c>
       <x:c r="L37" s="61" t="str">
         <x:v>German comparisons use the comparative adjective plus 'als.'</x:v>
@@ -3893,9 +3823,7 @@
       <x:c r="E38" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F38" s="61" t="str">
-        <x:v>Den Schaden sofort dem Vermieter melden</x:v>
-      </x:c>
+      <x:c r="F38" s="61"/>
       <x:c r="G38" s="61" t="str">
         <x:v>Den Schaden sofort dem Vermieter melden</x:v>
       </x:c>
@@ -3909,7 +3837,7 @@
         <x:v>Einen neuen Schrank kaufen</x:v>
       </x:c>
       <x:c r="K38" s="61" t="str">
-        <x:v>A</x:v>
+        <x:v>Den Schaden sofort dem Vermieter melden</x:v>
       </x:c>
       <x:c r="L38" s="61" t="str">
         <x:v>Reporting the damage promptly helps prevent further damage and allows repairs to begin.</x:v>
@@ -3931,9 +3859,7 @@
       <x:c r="E39" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F39" s="61" t="str">
-        <x:v>Heizung; WLAN; Fenster</x:v>
-      </x:c>
+      <x:c r="F39" s="61"/>
       <x:c r="G39" s="61" t="str">
         <x:v>Heizung</x:v>
       </x:c>
@@ -3947,7 +3873,7 @@
         <x:v>Lieblingsrestaurant</x:v>
       </x:c>
       <x:c r="K39" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Heizung; WLAN; Fenster</x:v>
       </x:c>
       <x:c r="L39" s="61" t="str">
         <x:v>Heating, internet availability, and windows are practical things to inspect.</x:v>
@@ -3969,9 +3895,7 @@
       <x:c r="E40" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F40" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F40" s="61"/>
       <x:c r="G40" s="61"/>
       <x:c r="H40" s="61"/>
       <x:c r="I40" s="61"/>
@@ -3999,9 +3923,7 @@
       <x:c r="E41" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F41" s="61" t="str">
-        <x:v>Briefträger</x:v>
-      </x:c>
+      <x:c r="F41" s="61"/>
       <x:c r="G41" s="61"/>
       <x:c r="H41" s="61"/>
       <x:c r="I41" s="61"/>
@@ -4029,9 +3951,7 @@
       <x:c r="E42" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F42" s="61" t="str">
-        <x:v>Den unterschriebenen Mietvertrag</x:v>
-      </x:c>
+      <x:c r="F42" s="61"/>
       <x:c r="G42" s="61" t="str">
         <x:v>Eine Restaurantrechnung</x:v>
       </x:c>
@@ -4045,7 +3965,7 @@
         <x:v>Einen Einkaufszettel</x:v>
       </x:c>
       <x:c r="K42" s="61" t="str">
-        <x:v>B</x:v>
+        <x:v>Den unterschriebenen Mietvertrag</x:v>
       </x:c>
       <x:c r="L42" s="61" t="str">
         <x:v>Keep a copy of the signed Mietvertrag in case questions arise after the tenancy ends.</x:v>
@@ -4067,9 +3987,7 @@
       <x:c r="E43" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F43" s="61" t="str">
-        <x:v>Report leaks quickly; Replace smoke detector batteries if required; Keep the apartment clean</x:v>
-      </x:c>
+      <x:c r="F43" s="61"/>
       <x:c r="G43" s="61" t="str">
         <x:v>Report leaks quickly</x:v>
       </x:c>
@@ -4083,7 +4001,7 @@
         <x:v>Ignore mold</x:v>
       </x:c>
       <x:c r="K43" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Report leaks quickly; Replace smoke detector batteries if required; Keep the apartment clean</x:v>
       </x:c>
       <x:c r="L43" s="61" t="str">
         <x:v>Prompt maintenance and cleanliness help protect both the apartment and your health.</x:v>
@@ -4105,9 +4023,7 @@
       <x:c r="E44" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F44" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F44" s="61"/>
       <x:c r="G44" s="61"/>
       <x:c r="H44" s="61"/>
       <x:c r="I44" s="61"/>
@@ -4135,9 +4051,7 @@
       <x:c r="E45" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F45" s="61" t="str">
-        <x:v>Tag</x:v>
-      </x:c>
+      <x:c r="F45" s="61"/>
       <x:c r="G45" s="61"/>
       <x:c r="H45" s="61"/>
       <x:c r="I45" s="61"/>
@@ -4165,9 +4079,7 @@
       <x:c r="E46" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F46" s="61" t="str">
-        <x:v>Wann werden die Reparaturen abgeschlossen?</x:v>
-      </x:c>
+      <x:c r="F46" s="61"/>
       <x:c r="G46" s="61" t="str">
         <x:v>Ich gehe jetzt.</x:v>
       </x:c>
@@ -4181,7 +4093,7 @@
         <x:v>Das dauert zu lange!</x:v>
       </x:c>
       <x:c r="K46" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Wann werden die Reparaturen abgeschlossen?</x:v>
       </x:c>
       <x:c r="L46" s="61" t="str">
         <x:v>This politely asks when the repair work will be finished.</x:v>
@@ -4203,9 +4115,7 @@
       <x:c r="E47" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F47" s="61" t="str">
-        <x:v>Reduce moisture; Improve air quality; Help prevent mold</x:v>
-      </x:c>
+      <x:c r="F47" s="61"/>
       <x:c r="G47" s="61" t="str">
         <x:v>Reduce moisture</x:v>
       </x:c>
@@ -4219,7 +4129,7 @@
         <x:v>Increase rent</x:v>
       </x:c>
       <x:c r="K47" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Reduce moisture; Improve air quality; Help prevent mold</x:v>
       </x:c>
       <x:c r="L47" s="61" t="str">
         <x:v>Ventilation improves comfort and helps prevent moisture-related problems.</x:v>
@@ -4241,9 +4151,7 @@
       <x:c r="E48" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F48" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F48" s="61"/>
       <x:c r="G48" s="61"/>
       <x:c r="H48" s="61"/>
       <x:c r="I48" s="61"/>
@@ -4271,9 +4179,7 @@
       <x:c r="E49" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F49" s="61" t="str">
-        <x:v>hell</x:v>
-      </x:c>
+      <x:c r="F49" s="61"/>
       <x:c r="G49" s="61"/>
       <x:c r="H49" s="61"/>
       <x:c r="I49" s="61"/>
@@ -4301,9 +4207,7 @@
       <x:c r="E50" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F50" s="61" t="str">
-        <x:v>ruhig</x:v>
-      </x:c>
+      <x:c r="F50" s="61"/>
       <x:c r="G50" s="61" t="str">
         <x:v>modern</x:v>
       </x:c>
@@ -4317,7 +4221,7 @@
         <x:v>ruhig</x:v>
       </x:c>
       <x:c r="K50" s="61" t="str">
-        <x:v>D</x:v>
+        <x:v>ruhig</x:v>
       </x:c>
       <x:c r="L50" s="61" t="str">
         <x:v>'Ruhig' means quiet and is commonly used in apartment advertisements.</x:v>
@@ -4339,9 +4243,7 @@
       <x:c r="E51" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F51" s="61" t="str">
-        <x:v>Balcony; Good internet; Natural light</x:v>
-      </x:c>
+      <x:c r="F51" s="61"/>
       <x:c r="G51" s="61" t="str">
         <x:v>Balcony</x:v>
       </x:c>
@@ -4355,7 +4257,7 @@
         <x:v>Broken heating</x:v>
       </x:c>
       <x:c r="K51" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Balcony; Good internet; Natural light</x:v>
       </x:c>
       <x:c r="L51" s="61" t="str">
         <x:v>These are common desirable features when choosing an apartment.</x:v>
@@ -4377,9 +4279,7 @@
       <x:c r="E52" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F52" s="61" t="str">
-        <x:v>Das Übergabeprotokoll</x:v>
-      </x:c>
+      <x:c r="F52" s="61"/>
       <x:c r="G52" s="61" t="str">
         <x:v>Der Internetvertrag</x:v>
       </x:c>
@@ -4393,7 +4293,7 @@
         <x:v>Die Fahrkarte</x:v>
       </x:c>
       <x:c r="K52" s="61" t="str">
-        <x:v>B</x:v>
+        <x:v>Das Übergabeprotokoll</x:v>
       </x:c>
       <x:c r="L52" s="61" t="str">
         <x:v>An Übergabeprotokoll documents the apartment's condition, defects, keys, and often meter readings at move-in.</x:v>
@@ -4415,9 +4315,7 @@
       <x:c r="E53" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F53" s="61" t="str">
-        <x:v>Existing wall damage; Meter readings; Kitchen appliances</x:v>
-      </x:c>
+      <x:c r="F53" s="61"/>
       <x:c r="G53" s="61" t="str">
         <x:v>Existing wall damage</x:v>
       </x:c>
@@ -4431,7 +4329,7 @@
         <x:v>Favorite café</x:v>
       </x:c>
       <x:c r="K53" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Existing wall damage; Meter readings; Kitchen appliances</x:v>
       </x:c>
       <x:c r="L53" s="61" t="str">
         <x:v>Photographs create a record of the apartment's condition and utility readings.</x:v>
@@ -4453,9 +4351,7 @@
       <x:c r="E54" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F54" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F54" s="61"/>
       <x:c r="G54" s="61"/>
       <x:c r="H54" s="61"/>
       <x:c r="I54" s="61"/>
@@ -4483,9 +4379,7 @@
       <x:c r="E55" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F55" s="61" t="str">
-        <x:v>besichtigung</x:v>
-      </x:c>
+      <x:c r="F55" s="61"/>
       <x:c r="G55" s="61"/>
       <x:c r="H55" s="61"/>
       <x:c r="I55" s="61"/>
@@ -4513,9 +4407,7 @@
       <x:c r="E56" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F56" s="61" t="str">
-        <x:v>Könnten Sie das bitte erklären?</x:v>
-      </x:c>
+      <x:c r="F56" s="61"/>
       <x:c r="G56" s="61" t="str">
         <x:v>Das ist egal.</x:v>
       </x:c>
@@ -4529,7 +4421,7 @@
         <x:v>Ich gehe jetzt.</x:v>
       </x:c>
       <x:c r="K56" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Könnten Sie das bitte erklären?</x:v>
       </x:c>
       <x:c r="L56" s="61" t="str">
         <x:v>Politely asking for clarification helps you understand your rights and responsibilities before signing.</x:v>
@@ -4551,9 +4443,7 @@
       <x:c r="E57" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F57" s="61" t="str">
-        <x:v>Arrange internet; Read the lease; Check smoke detectors</x:v>
-      </x:c>
+      <x:c r="F57" s="61"/>
       <x:c r="G57" s="61" t="str">
         <x:v>Arrange internet</x:v>
       </x:c>
@@ -4567,7 +4457,7 @@
         <x:v>Ignore utility setup</x:v>
       </x:c>
       <x:c r="K57" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Arrange internet; Read the lease; Check smoke detectors</x:v>
       </x:c>
       <x:c r="L57" s="61" t="str">
         <x:v>Preparing utilities and checking safety equipment makes the move smoother.</x:v>
@@ -4589,9 +4479,7 @@
       <x:c r="E58" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F58" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F58" s="61"/>
       <x:c r="G58" s="61"/>
       <x:c r="H58" s="61"/>
       <x:c r="I58" s="61"/>
@@ -4619,9 +4507,7 @@
       <x:c r="E59" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F59" s="61" t="str">
-        <x:v>durchgeführt</x:v>
-      </x:c>
+      <x:c r="F59" s="61"/>
       <x:c r="G59" s="61"/>
       <x:c r="H59" s="61"/>
       <x:c r="I59" s="61"/>
@@ -4649,9 +4535,7 @@
       <x:c r="E60" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F60" s="61" t="str">
-        <x:v>Gibt es schon ein Update zur Reparatur?</x:v>
-      </x:c>
+      <x:c r="F60" s="61"/>
       <x:c r="G60" s="61" t="str">
         <x:v>Ich kündige sofort.</x:v>
       </x:c>
@@ -4665,7 +4549,7 @@
         <x:v>Warum dauert das so lange?</x:v>
       </x:c>
       <x:c r="K60" s="61" t="str">
-        <x:v>B</x:v>
+        <x:v>Gibt es schon ein Update zur Reparatur?</x:v>
       </x:c>
       <x:c r="L60" s="61" t="str">
         <x:v>This is a courteous way to ask about the current status of a repair.</x:v>
@@ -4687,9 +4571,7 @@
       <x:c r="E61" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F61" s="61" t="str">
-        <x:v>Return all keys; Leave the apartment clean; Record final meter readings</x:v>
-      </x:c>
+      <x:c r="F61" s="61"/>
       <x:c r="G61" s="61" t="str">
         <x:v>Return all keys</x:v>
       </x:c>
@@ -4703,7 +4585,7 @@
         <x:v>Take the smoke detector</x:v>
       </x:c>
       <x:c r="K61" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Return all keys; Leave the apartment clean; Record final meter readings</x:v>
       </x:c>
       <x:c r="L61" s="61" t="str">
         <x:v>Returning keys, cleaning, and recording utilities are common move-out responsibilities.</x:v>
@@ -4725,9 +4607,7 @@
       <x:c r="E62" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F62" s="61" t="str">
-        <x:v>Haftpflichtversicherung</x:v>
-      </x:c>
+      <x:c r="F62" s="61"/>
       <x:c r="G62" s="61" t="str">
         <x:v>Krankenversicherung</x:v>
       </x:c>
@@ -4741,7 +4621,7 @@
         <x:v>Haftpflichtversicherung</x:v>
       </x:c>
       <x:c r="K62" s="61" t="str">
-        <x:v>D</x:v>
+        <x:v>Haftpflichtversicherung</x:v>
       </x:c>
       <x:c r="L62" s="61" t="str">
         <x:v>Haftpflichtversicherung covers many accidental damages caused to other people or their property.</x:v>
@@ -4763,9 +4643,7 @@
       <x:c r="E63" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F63" s="61" t="str">
-        <x:v>Persistent mold; Leaking roof; Broken heating</x:v>
-      </x:c>
+      <x:c r="F63" s="61"/>
       <x:c r="G63" s="61" t="str">
         <x:v>Persistent mold</x:v>
       </x:c>
@@ -4779,7 +4657,7 @@
         <x:v>A cloudy day</x:v>
       </x:c>
       <x:c r="K63" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Persistent mold; Leaking roof; Broken heating</x:v>
       </x:c>
       <x:c r="L63" s="61" t="str">
         <x:v>Structural problems and failed building systems should be reported promptly.</x:v>
@@ -4801,9 +4679,7 @@
       <x:c r="E64" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F64" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F64" s="61"/>
       <x:c r="G64" s="61"/>
       <x:c r="H64" s="61"/>
       <x:c r="I64" s="61"/>
@@ -4831,9 +4707,7 @@
       <x:c r="E65" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F65" s="61" t="str">
-        <x:v>Mietvertrag</x:v>
-      </x:c>
+      <x:c r="F65" s="61"/>
       <x:c r="G65" s="61"/>
       <x:c r="H65" s="61"/>
       <x:c r="I65" s="61"/>
@@ -4861,9 +4735,7 @@
       <x:c r="E66" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F66" s="61" t="str">
-        <x:v>Ist die Wohnung noch frei?</x:v>
-      </x:c>
+      <x:c r="F66" s="61"/>
       <x:c r="G66" s="61" t="str">
         <x:v>Wann fährt der Bus?</x:v>
       </x:c>
@@ -4877,7 +4749,7 @@
         <x:v>Wie alt sind Sie?</x:v>
       </x:c>
       <x:c r="K66" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Ist die Wohnung noch frei?</x:v>
       </x:c>
       <x:c r="L66" s="61" t="str">
         <x:v>'Ist die Wohnung noch frei?' is a common question when contacting a landlord about a listing.</x:v>
@@ -4899,9 +4771,7 @@
       <x:c r="E67" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F67" s="61" t="str">
-        <x:v>Clean the apartment; Return every key; Take final photos</x:v>
-      </x:c>
+      <x:c r="F67" s="61"/>
       <x:c r="G67" s="61" t="str">
         <x:v>Clean the apartment</x:v>
       </x:c>
@@ -4915,7 +4785,7 @@
         <x:v>Leave personal furniture</x:v>
       </x:c>
       <x:c r="K67" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Clean the apartment; Return every key; Take final photos</x:v>
       </x:c>
       <x:c r="L67" s="61" t="str">
         <x:v>Cleaning, returning keys, and documenting the condition help complete the tenancy smoothly.</x:v>
@@ -4937,9 +4807,7 @@
       <x:c r="E68" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F68" s="61" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="F68" s="61"/>
       <x:c r="G68" s="61"/>
       <x:c r="H68" s="61"/>
       <x:c r="I68" s="61"/>
@@ -4967,9 +4835,7 @@
       <x:c r="E69" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F69" s="61" t="str">
-        <x:v>gelegen</x:v>
-      </x:c>
+      <x:c r="F69" s="61"/>
       <x:c r="G69" s="61"/>
       <x:c r="H69" s="61"/>
       <x:c r="I69" s="61"/>
@@ -4997,9 +4863,7 @@
       <x:c r="E70" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F70" s="61" t="str">
-        <x:v>Sind Haustiere erlaubt?</x:v>
-      </x:c>
+      <x:c r="F70" s="61"/>
       <x:c r="G70" s="61" t="str">
         <x:v>Wo ist der Park?</x:v>
       </x:c>
@@ -5013,7 +4877,7 @@
         <x:v>Ich bringe meinen Hund.</x:v>
       </x:c>
       <x:c r="K70" s="61" t="str">
-        <x:v>C</x:v>
+        <x:v>Sind Haustiere erlaubt?</x:v>
       </x:c>
       <x:c r="L70" s="61" t="str">
         <x:v>This is the standard polite question to ask before signing a lease.</x:v>
@@ -5035,9 +4899,7 @@
       <x:c r="E71" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F71" s="61" t="str">
-        <x:v>Monthly cost; Location; Condition</x:v>
-      </x:c>
+      <x:c r="F71" s="61"/>
       <x:c r="G71" s="61" t="str">
         <x:v>Monthly cost</x:v>
       </x:c>
@@ -5051,7 +4913,7 @@
         <x:v>Favorite TV show</x:v>
       </x:c>
       <x:c r="K71" s="61" t="str">
-        <x:v>A,B,C</x:v>
+        <x:v>Monthly cost; Location; Condition</x:v>
       </x:c>
       <x:c r="L71" s="61" t="str">
         <x:v>Comparing cost, location, and condition helps you choose the most suitable apartment.</x:v>
@@ -5073,9 +4935,7 @@
       <x:c r="E72" s="61" t="str">
         <x:v>Choose True or False.</x:v>
       </x:c>
-      <x:c r="F72" s="61" t="str">
-        <x:v>True</x:v>
-      </x:c>
+      <x:c r="F72" s="61"/>
       <x:c r="G72" s="61"/>
       <x:c r="H72" s="61"/>
       <x:c r="I72" s="61"/>
@@ -5103,9 +4963,7 @@
       <x:c r="E73" s="61" t="str">
         <x:v>Complete the sentence.</x:v>
       </x:c>
-      <x:c r="F73" s="61" t="str">
-        <x:v>Kaution</x:v>
-      </x:c>
+      <x:c r="F73" s="61"/>
       <x:c r="G73" s="61"/>
       <x:c r="H73" s="61"/>
       <x:c r="I73" s="61"/>
@@ -5133,9 +4991,7 @@
       <x:c r="E74" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F74" s="61" t="str">
-        <x:v>Den Schaden umgehend dem Vermieter melden</x:v>
-      </x:c>
+      <x:c r="F74" s="61"/>
       <x:c r="G74" s="61" t="str">
         <x:v>Den Schaden umgehend dem Vermieter melden</x:v>
       </x:c>
@@ -5149,7 +5005,7 @@
         <x:v>Einen Touristen fragen</x:v>
       </x:c>
       <x:c r="K74" s="61" t="str">
-        <x:v>A</x:v>
+        <x:v>Den Schaden umgehend dem Vermieter melden</x:v>
       </x:c>
       <x:c r="L74" s="61" t="str">
         <x:v>Prompt communication helps prevent additional damage and allows the landlord to arrange repairs.</x:v>
@@ -5171,9 +5027,7 @@
       <x:c r="E75" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F75" s="61" t="str">
-        <x:v>Renting an apartment; Reporting repairs; Understanding lease terms; Living responsibly with neighbors</x:v>
-      </x:c>
+      <x:c r="F75" s="61"/>
       <x:c r="G75" s="61" t="str">
         <x:v>Renting an apartment</x:v>
       </x:c>
@@ -5187,7 +5041,7 @@
         <x:v>Living responsibly with neighbors</x:v>
       </x:c>
       <x:c r="K75" s="61" t="str">
-        <x:v>A,B,C,D</x:v>
+        <x:v>Renting an apartment; Reporting repairs; Understanding lease terms; Living responsibly with neighbors</x:v>
       </x:c>
       <x:c r="L75" s="61" t="str">
         <x:v>Unit 4 combines housing vocabulary, communication, grammar, and practical living skills.</x:v>
@@ -5209,9 +5063,7 @@
       <x:c r="E76" s="61" t="str">
         <x:v>Choose the correct answer.</x:v>
       </x:c>
-      <x:c r="F76" s="61" t="str">
-        <x:v>Das Deutsch lernen, das man zum Finden, Mieten und Bewohnen einer Wohnung braucht</x:v>
-      </x:c>
+      <x:c r="F76" s="61"/>
       <x:c r="G76" s="61" t="str">
         <x:v>Deutsche Literatur analysieren</x:v>
       </x:c>
@@ -5225,7 +5077,7 @@
         <x:v>Das Deutsch lernen, das man zum Finden, Mieten und Bewohnen einer Wohnung braucht</x:v>
       </x:c>
       <x:c r="K76" s="61" t="str">
-        <x:v>D</x:v>
+        <x:v>Das Deutsch lernen, das man zum Finden, Mieten und Bewohnen einer Wohnung braucht</x:v>
       </x:c>
       <x:c r="L76" s="61" t="str">
         <x:v>Unit 4 prepares learners to find, rent, maintain, and live responsibly in an apartment in Germany.</x:v>
@@ -5247,9 +5099,7 @@
       <x:c r="E77" s="61" t="str">
         <x:v>Select all correct answers.</x:v>
       </x:c>
-      <x:c r="F77" s="61" t="str">
-        <x:v>Den Vermieter oder Hausmeister informieren; Das Problem schriftlich dokumentieren; Nach einer Reparaturmöglichkeit fragen</x:v>
-      </x:c>
+      <x:c r="F77" s="61"/>
       <x:c r="G77" s="61" t="str">
         <x:v>Den Vermieter oder Hausmeister informieren</x:v>
       </x:c>
@@ -5263,7 +5113,7 @@
         <x:v>Nach einer Reparaturmöglichkeit fragen</x:v>
       </x:c>
       <x:c r="K77" s="61" t="str">
-        <x:v>A,B,D</x:v>
+        <x:v>Den Vermieter oder Hausmeister informieren; Das Problem schriftlich dokumentieren; Nach einer Reparaturmöglichkeit fragen</x:v>
       </x:c>
       <x:c r="L77" s="61" t="str">
         <x:v>You should report and document the problem and ask how it will be repaired while still respecting the building's quiet-hour rules.</x:v>
